--- a/data/trans_orig/IP1022_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>47581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72130</t>
+          <t>72116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69986</t>
+          <t>70383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77754</t>
+          <t>77770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116873</t>
+          <t>118752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148155</t>
+          <t>147876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111255</t>
+          <t>111737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123457</t>
+          <t>123713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115340</t>
+          <t>115385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124609</t>
+          <t>124705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>231317</t>
+          <t>231169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>245919</t>
+          <t>245807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50437</t>
+          <t>51067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56666</t>
+          <t>56747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55852</t>
+          <t>55220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63630</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109521</t>
+          <t>109403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119057</t>
+          <t>119743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59206</t>
+          <t>59447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67916</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60127</t>
+          <t>60635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74026</t>
+          <t>74120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124324</t>
+          <t>124669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139642</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33979</t>
+          <t>33987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40181</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67597</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37645</t>
+          <t>37507</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>43643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53555</t>
+          <t>53545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86291</t>
+          <t>86492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96013</t>
+          <t>96411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48758</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107679</t>
+          <t>107537</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118432</t>
+          <t>118581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110661</t>
+          <t>113785</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139908</t>
+          <t>140540</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227527</t>
+          <t>225328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256341</t>
+          <t>255061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124578</t>
+          <t>124817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130998</t>
+          <t>130999</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149370</t>
+          <t>149025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155650</t>
+          <t>155700</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>277711</t>
+          <t>276647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285840</t>
+          <t>285892</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62818</t>
+          <t>64667</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79980</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83732</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>130841</t>
+          <t>130132</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>601914</t>
+          <t>600065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>633229</t>
+          <t>632432</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>677756</t>
+          <t>679269</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>712282</t>
+          <t>713705</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1291627</t>
+          <t>1292336</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1338736</t>
+          <t>1339219</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1022_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25701</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60205</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55787</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62417</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>65711</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47581</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72116</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>75005</t>
+          <t>53982</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70383</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>55899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>140715</t>
+          <t>114187</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118752</t>
+          <t>109530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147876</t>
+          <t>117682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2359</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11404</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8581</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3126</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15102</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23266</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>104431</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>113476</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>118258</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111737</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>123713</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>121528</t>
+          <t>91746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115385</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124705</t>
+          <t>95971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>239785</t>
+          <t>202052</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>231169</t>
+          <t>194168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>245807</t>
+          <t>207717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3625</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1521</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7201</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53426</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49861</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56566</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>54643</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>51067</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56747</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60451</t>
+          <t>52894</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55220</t>
+          <t>49450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63538</t>
+          <t>55030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>115094</t>
+          <t>106321</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109403</t>
+          <t>100883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119743</t>
+          <t>109895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9012</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3994</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16794</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5447</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2392</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10696</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63150</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55368</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68168</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>64696</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>59447</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>67751</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68570</t>
+          <t>64712</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60635</t>
+          <t>59119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74120</t>
+          <t>68253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>133266</t>
+          <t>127860</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124669</t>
+          <t>119107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>134415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5076</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4472</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2268</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5111</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>37430</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34503</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38997</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>32863</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>30041</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33987</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>33878</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>31097</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35064</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>95,14%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>98,47%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>38451</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>35608</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>87,45%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>132</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>71314</t>
+          <t>71308</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>67230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>73568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8898</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4138</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8052</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43891</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>40044</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>46699</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>81,82%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>41421</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>37507</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>43643</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>82,33%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>41030</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53545</t>
+          <t>43314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>92198</t>
+          <t>84921</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86492</t>
+          <t>79917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96411</t>
+          <t>88631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>45559</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>45559</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>45559</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>94038</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>94038</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>94038</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14009</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8415</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21284</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>10426</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5927</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>16971</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>13,63%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37991</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21224</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>122989</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>115714</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>128583</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>89,77%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>114082</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>107537</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>118581</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>86,37%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>131793</t>
+          <t>111752</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113785</t>
+          <t>105412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>140540</t>
+          <t>116437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>245876</t>
+          <t>234741</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225328</t>
+          <t>225731</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>255061</t>
+          <t>242564</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>151776</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>151776</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151776</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>276285</t>
+          <t>259527</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276285</t>
+          <t>259527</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>276285</t>
+          <t>259527</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3384</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7848</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2365</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6802</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>156037</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>151573</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>158496</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>95,08%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>129254</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>124817</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>130999</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>94,83%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>153533</t>
+          <t>137863</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149025</t>
+          <t>133426</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155700</t>
+          <t>139776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>282787</t>
+          <t>293900</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>276647</t>
+          <t>287838</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285892</t>
+          <t>297274</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>49026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>38275</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>63224</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>43804</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>64667</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83249</t>
+          <t>74610</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>130132</t>
+          <t>106578</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>647434</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>633236</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>658185</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>884</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>620928</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>600065</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>632432</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>700108</t>
+          <t>587856</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>679269</t>
+          <t>576067</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>713705</t>
+          <t>597419</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1321036</t>
+          <t>1235291</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1292336</t>
+          <t>1218045</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1339219</t>
+          <t>1250013</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>664732</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>628163</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1422468</t>
+          <t>1324623</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
